--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_d_enveje_a_2020_antofagasta.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_d_enveje_a_2020_antofagasta.xlsx
@@ -120,7 +120,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 14:08</t>
+    <t xml:space="preserve">2026-09-24 00:59</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -561,10 +561,10 @@
         <v>-0.08</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
     </row>
     <row r="3">
@@ -575,7 +575,7 @@
         <v>8</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>-0.03</v>
+        <v>-0.02</v>
       </c>
       <c r="D3" s="2" t="n">
         <v>6</v>
@@ -584,10 +584,10 @@
         <v>-0.16</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
     </row>
     <row r="4">
@@ -607,7 +607,7 @@
         <v>0.02</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="G4" s="2" t="n">
         <v>0.11</v>
@@ -621,7 +621,7 @@
         <v>8</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>-0.21</v>
+        <v>-0.22</v>
       </c>
       <c r="D5" s="2" t="n">
         <v>6</v>
@@ -630,10 +630,10 @@
         <v>0.17</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>-0.38</v>
+        <v>-0.39</v>
       </c>
     </row>
     <row r="6">
@@ -644,7 +644,7 @@
         <v>8</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>-0.57</v>
+        <v>-0.58</v>
       </c>
       <c r="D6" s="2" t="n">
         <v>6</v>
@@ -653,10 +653,10 @@
         <v>0.21</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>-0.78</v>
+        <v>-0.79</v>
       </c>
     </row>
     <row r="7">
@@ -676,10 +676,10 @@
         <v>-0.05</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>0.78</v>
+        <v>0.77</v>
       </c>
     </row>
     <row r="8">
@@ -696,13 +696,13 @@
         <v>9</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>-0.2</v>
+        <v>-0.19</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>0.26</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="9">
@@ -713,19 +713,19 @@
         <v>14</v>
       </c>
       <c r="C9" s="2" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="D9" s="2" t="n">
         <v>9</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>-0.23</v>
+        <v>-0.22</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
     </row>
     <row r="10">
@@ -743,7 +743,7 @@
         <v>-0.13</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="G10" s="2"/>
     </row>
@@ -762,7 +762,7 @@
         <v>-0.13</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="G11" s="2"/>
     </row>
@@ -783,10 +783,10 @@
         <v>0.11</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="13">
@@ -797,19 +797,19 @@
         <v>14</v>
       </c>
       <c r="C13" s="2" t="n">
-        <v>0.33</v>
+        <v>0.32</v>
       </c>
       <c r="D13" s="2" t="n">
         <v>8</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>0.06</v>
+        <v>0.07</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>0.26</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="14">
@@ -826,10 +826,10 @@
         <v>8</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="G14" s="2" t="n">
         <v>-0.09</v>
@@ -843,16 +843,16 @@
         <v>14</v>
       </c>
       <c r="C15" s="2" t="n">
-        <v>0.45</v>
+        <v>0.44</v>
       </c>
       <c r="D15" s="2" t="n">
         <v>9</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>-0.06</v>
+        <v>-0.07</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="G15" s="2" t="n">
         <v>0.51</v>
@@ -875,7 +875,7 @@
         <v>0.22</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="G16" s="2" t="n">
         <v>0.24</v>
@@ -889,7 +889,7 @@
         <v>14</v>
       </c>
       <c r="C17" s="2" t="n">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="D17" s="2" t="n">
         <v>9</v>
@@ -898,10 +898,10 @@
         <v>0.05</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
     </row>
     <row r="18">
@@ -912,7 +912,7 @@
         <v>26</v>
       </c>
       <c r="C18" s="2" t="n">
-        <v>-0.19</v>
+        <v>-0.18</v>
       </c>
       <c r="D18" s="2" t="n">
         <v>6</v>
@@ -921,10 +921,10 @@
         <v>-0.32</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
     </row>
     <row r="19">
@@ -944,7 +944,7 @@
         <v>0.23</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="G19" s="2" t="n">
         <v>-0.95</v>
@@ -964,13 +964,13 @@
         <v>9</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>-0.72</v>
+        <v>-0.71</v>
       </c>
     </row>
     <row r="21">
@@ -990,10 +990,10 @@
         <v>0.01</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>-0.22</v>
+        <v>-0.23</v>
       </c>
     </row>
   </sheetData>

--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_d_enveje_a_2020_antofagasta.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_d_enveje_a_2020_antofagasta.xlsx
@@ -105,7 +105,7 @@
     <t xml:space="preserve">Migración</t>
   </si>
   <si>
-    <t xml:space="preserve">Movilidad interna (CMI)</t>
+    <t xml:space="preserve">Movilidad interna comunal (CMI)</t>
   </si>
   <si>
     <t xml:space="preserve">Saldo migratorio</t>
@@ -120,7 +120,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-24 00:59</t>
+    <t xml:space="preserve">2026-10-01 23:06</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_d_enveje_a_2020_antofagasta.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_d_enveje_a_2020_antofagasta.xlsx
@@ -120,7 +120,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-01 23:06</t>
+    <t xml:space="preserve">2026-10-05 19:38</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
